--- a/Book2.xlsx
+++ b/Book2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPELILLO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D932A7F-1F1A-470F-973A-448156D8A6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445F939B-3673-4D9C-AE40-B689755B5B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BC2DADC9-37AA-4A30-A1BE-5B381AFE2D2F}"/>
   </bookViews>
@@ -38,8 +38,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={B81AFD1D-5683-4614-98CE-4135AADEAC1B}</author>
+  </authors>
+  <commentList>
+    <comment ref="F38" authorId="0" shapeId="0" xr:uid="{B81AFD1D-5683-4614-98CE-4135AADEAC1B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    1.4x</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
   <si>
     <t>Loan</t>
   </si>
@@ -165,19 +183,61 @@
   </si>
   <si>
     <t>Remainder for business</t>
+  </si>
+  <si>
+    <t>non-loan totals</t>
+  </si>
+  <si>
+    <t>owner</t>
+  </si>
+  <si>
+    <t>total non-loan</t>
+  </si>
+  <si>
+    <t>comission</t>
+  </si>
+  <si>
+    <t>y1</t>
+  </si>
+  <si>
+    <t>y2</t>
+  </si>
+  <si>
+    <t>starting cash on hand</t>
+  </si>
+  <si>
+    <t>expenses</t>
+  </si>
+  <si>
+    <t>revenue</t>
+  </si>
+  <si>
+    <t>profit</t>
+  </si>
+  <si>
+    <t>y3</t>
+  </si>
+  <si>
+    <t>y4</t>
+  </si>
+  <si>
+    <t>y5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="7">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="173" formatCode="0.000"/>
     <numFmt numFmtId="179" formatCode="0.000%"/>
+    <numFmt numFmtId="182" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="184" formatCode="_(&quot;$&quot;* #,##0.000_);_(&quot;$&quot;* \(#,##0.000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,6 +277,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u val="singleAccounting"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -244,7 +320,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -270,12 +346,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -283,7 +369,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -318,7 +404,7 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -331,7 +417,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -342,13 +428,28 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="9">
     <dxf>
@@ -426,6 +527,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Pelillo, Sean R (CGI Federal)" id="{B8454F4E-1D39-4330-A3D5-B846FA7F93AE}" userId="S::sean.pelillo@cgifederal.com::c8b6a834-ba55-4a2b-9e6e-91519103adbe" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -743,9 +850,17 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="F38" dT="2026-10-26T18:33:09.14" personId="{B8454F4E-1D39-4330-A3D5-B846FA7F93AE}" id="{B81AFD1D-5683-4614-98CE-4135AADEAC1B}">
+    <text>1.4x</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F1F4FE-9889-4545-8ED4-BDD62AF4ACF5}">
-  <dimension ref="B1:G29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F1F4FE-9889-4545-8ED4-BDD62AF4ACF5}">
+  <dimension ref="B1:J39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
@@ -754,6 +869,8 @@
     <col min="5" max="5" width="27.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.3">
@@ -762,7 +879,7 @@
       </c>
       <c r="C1" s="3">
         <f>-$C$5*1.16</f>
-        <v>406000</v>
+        <v>696000</v>
       </c>
       <c r="E1" s="15" t="s">
         <v>27</v>
@@ -779,8 +896,8 @@
         <v>1</v>
       </c>
       <c r="C2" s="5">
-        <f>F2</f>
-        <v>7.4999999999999997E-2</v>
+        <f>E2</f>
+        <v>5.5E-2</v>
       </c>
       <c r="E2" s="25">
         <v>5.5E-2</v>
@@ -798,7 +915,7 @@
       </c>
       <c r="C3" s="3">
         <f>C1*(1+C2)</f>
-        <v>436450</v>
+        <v>734280</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -811,7 +928,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="18">
-        <v>-350000</v>
+        <v>-600000</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="22" t="s">
@@ -830,7 +947,7 @@
       </c>
       <c r="C6" s="3">
         <f>C5*F6</f>
-        <v>-61249.999999999993</v>
+        <v>-105000</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>12</v>
@@ -850,8 +967,8 @@
         <v>7</v>
       </c>
       <c r="C7" s="3">
-        <f>-$C$1</f>
-        <v>-406000</v>
+        <f>-C1</f>
+        <v>-696000</v>
       </c>
       <c r="D7" s="9"/>
     </row>
@@ -860,8 +977,8 @@
         <v>6</v>
       </c>
       <c r="C8" s="3">
-        <f>$C$1-$C$3</f>
-        <v>-30450</v>
+        <f>-1*(C3-C1)</f>
+        <v>-38280</v>
       </c>
       <c r="D8" s="9"/>
     </row>
@@ -871,7 +988,7 @@
       </c>
       <c r="C9" s="3">
         <f>$C$5*D9</f>
-        <v>-10500</v>
+        <v>-18000</v>
       </c>
       <c r="D9" s="19">
         <v>0.03</v>
@@ -883,7 +1000,7 @@
       </c>
       <c r="C10" s="3">
         <f t="shared" ref="C10:C12" si="0">$C$5*D10</f>
-        <v>-5250</v>
+        <v>-9000</v>
       </c>
       <c r="D10" s="19">
         <v>1.4999999999999999E-2</v>
@@ -895,7 +1012,7 @@
       </c>
       <c r="C11" s="3">
         <f t="shared" si="0"/>
-        <v>-1400</v>
+        <v>-2400</v>
       </c>
       <c r="D11" s="19">
         <v>4.0000000000000001E-3</v>
@@ -907,7 +1024,7 @@
       </c>
       <c r="C12" s="3">
         <f t="shared" si="0"/>
-        <v>-2184</v>
+        <v>-3744</v>
       </c>
       <c r="D12" s="20">
         <v>6.2399999999999999E-3</v>
@@ -934,7 +1051,7 @@
       </c>
       <c r="C14" s="3">
         <f>$C$3*F14</f>
-        <v>545562.5</v>
+        <v>917850</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>14</v>
@@ -955,13 +1072,13 @@
       </c>
       <c r="C15" s="17">
         <f>-C14*E15</f>
-        <v>-5455.625</v>
+        <v>-20651.625</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="6">
-        <v>0.01</v>
+      <c r="E15" s="35">
+        <v>2.2499999999999999E-2</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.3">
@@ -970,49 +1087,50 @@
       </c>
       <c r="C16" s="17">
         <f>C5*D16</f>
-        <v>-3500</v>
+        <v>-6000</v>
       </c>
       <c r="D16" s="21">
         <v>0.01</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="17">
         <f>C5*D17</f>
-        <v>-3500</v>
+        <v>-6000</v>
       </c>
       <c r="D17" s="21">
         <v>0.01</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="17">
         <f>SUM(C5:C17)*D18</f>
-        <v>-10017.813749999999</v>
+        <v>-20552.896875000002</v>
       </c>
       <c r="D18" s="32">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="J18" s="34"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C19" s="18">
         <f>SUM(C1,C5:C18)</f>
-        <v>62055.061249999999</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+        <v>88221.478124999994</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C21" s="3" t="s">
         <v>31</v>
       </c>
@@ -1022,24 +1140,34 @@
       <c r="F21" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G21" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C22" s="28" t="s">
         <v>35</v>
       </c>
       <c r="D22" s="28">
         <f>C19</f>
-        <v>62055.061249999999</v>
+        <v>88221.478124999994</v>
       </c>
       <c r="E22" s="29">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="F22" s="27">
         <f>D22*E22</f>
-        <v>620550.61250000005</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+        <v>11909899.546875</v>
+      </c>
+      <c r="J22" s="34">
+        <f>1228534*15</f>
+        <v>18428010</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C23" s="3" t="s">
         <v>33</v>
       </c>
@@ -1047,14 +1175,14 @@
         <v>-55000</v>
       </c>
       <c r="E23" s="6">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="F23" s="2">
         <f>D23*E23</f>
-        <v>-165000</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+        <v>-3300000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C24" s="3" t="s">
         <v>37</v>
       </c>
@@ -1062,39 +1190,64 @@
         <v>-15000</v>
       </c>
       <c r="E24" s="6">
-        <v>3</v>
+        <f>E23</f>
+        <v>60</v>
       </c>
       <c r="F24" s="2">
         <f>D24*E24</f>
-        <v>-45000</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>-900000</v>
+      </c>
+      <c r="H24" t="s">
+        <v>45</v>
+      </c>
+      <c r="I24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C25" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D25" s="3">
         <f>C15</f>
-        <v>-5455.625</v>
+        <v>-20651.625</v>
       </c>
       <c r="E25" s="6">
-        <v>10</v>
+        <f>E22</f>
+        <v>135</v>
       </c>
       <c r="F25" s="26">
         <f>D25*E25</f>
-        <v>-54556.25</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>-2787969.375</v>
+      </c>
+      <c r="G25">
+        <v>15</v>
+      </c>
+      <c r="H25" s="3">
+        <v>3251</v>
+      </c>
+      <c r="I25" s="3">
+        <v>8202</v>
+      </c>
+      <c r="J25" s="3">
+        <f>-G25*(H25+I25)</f>
+        <v>-171795</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C26" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F26" s="27">
         <f>SUM(F22:F25)</f>
-        <v>355994.36250000005</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+        <v>4921930.171875</v>
+      </c>
+      <c r="J26" s="36">
+        <f>SUM(J22:J25)</f>
+        <v>18256215</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C27" s="3" t="s">
         <v>39</v>
       </c>
@@ -1103,30 +1256,31 @@
       </c>
       <c r="E27" s="7">
         <f>D27*F26</f>
-        <v>106798.30875000001</v>
+        <v>1476579.0515625</v>
       </c>
       <c r="F27" s="2">
         <f>F26*(1-D27)</f>
-        <v>249196.05375000002</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+        <v>3445351.1203124998</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C28" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D28" s="3">
         <f>C18</f>
-        <v>-10017.813749999999</v>
+        <v>-20552.896875000002</v>
       </c>
       <c r="E28" s="6">
         <v>10</v>
       </c>
       <c r="F28" s="2">
         <f>D28*E28</f>
-        <v>-100178.1375</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+        <v>-205528.96875000003</v>
+      </c>
+      <c r="J28" s="41"/>
+    </row>
+    <row r="29" spans="2:10" ht="16.2" x14ac:dyDescent="0.45">
       <c r="C29" s="3" t="s">
         <v>41</v>
       </c>
@@ -1138,7 +1292,131 @@
       </c>
       <c r="F29" s="31">
         <f>F27+F28</f>
-        <v>149017.91625000001</v>
+        <v>3239822.1515624998</v>
+      </c>
+      <c r="J29" s="40">
+        <f>F29+J26</f>
+        <v>21496037.151562501</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J30" s="42"/>
+    </row>
+    <row r="35" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="F35" t="s">
+        <v>46</v>
+      </c>
+      <c r="G35" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" t="s">
+        <v>52</v>
+      </c>
+      <c r="I35" t="s">
+        <v>53</v>
+      </c>
+      <c r="J35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="E36" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" s="33">
+        <v>30000000</v>
+      </c>
+      <c r="G36" s="33">
+        <f>F39</f>
+        <v>36000000</v>
+      </c>
+      <c r="H36" s="33">
+        <f>G39</f>
+        <v>43200000</v>
+      </c>
+      <c r="I36" s="33">
+        <f t="shared" ref="I36:J36" si="1">H39</f>
+        <v>51840000</v>
+      </c>
+      <c r="J36" s="33">
+        <f t="shared" ref="J36" si="2">I39</f>
+        <v>62208000</v>
+      </c>
+    </row>
+    <row r="37" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="D37" s="38"/>
+      <c r="E37" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="33">
+        <f>-0.5*F36</f>
+        <v>-15000000</v>
+      </c>
+      <c r="G37" s="33">
+        <f>-0.5*G36</f>
+        <v>-18000000</v>
+      </c>
+      <c r="H37" s="33">
+        <f t="shared" ref="H37:J37" si="3">-0.5*H36</f>
+        <v>-21600000</v>
+      </c>
+      <c r="I37" s="33">
+        <f t="shared" si="3"/>
+        <v>-25920000</v>
+      </c>
+      <c r="J37" s="33">
+        <f t="shared" si="3"/>
+        <v>-31104000</v>
+      </c>
+    </row>
+    <row r="38" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="E38" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F38" s="39">
+        <f>F37*-1.4</f>
+        <v>21000000</v>
+      </c>
+      <c r="G38" s="39">
+        <f>G37*-1.4</f>
+        <v>25200000</v>
+      </c>
+      <c r="H38" s="39">
+        <f t="shared" ref="H38:J38" si="4">H37*-1.4</f>
+        <v>30239999.999999996</v>
+      </c>
+      <c r="I38" s="39">
+        <f t="shared" si="4"/>
+        <v>36288000</v>
+      </c>
+      <c r="J38" s="39">
+        <f t="shared" si="4"/>
+        <v>43545600</v>
+      </c>
+    </row>
+    <row r="39" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="E39" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F39" s="33">
+        <f>SUM(F36:F38)</f>
+        <v>36000000</v>
+      </c>
+      <c r="G39" s="33">
+        <f>SUM(G36:G38)</f>
+        <v>43200000</v>
+      </c>
+      <c r="H39" s="33">
+        <f t="shared" ref="H39:J39" si="5">SUM(H36:H38)</f>
+        <v>51840000</v>
+      </c>
+      <c r="I39" s="33">
+        <f t="shared" si="5"/>
+        <v>62208000</v>
+      </c>
+      <c r="J39" s="33">
+        <f t="shared" si="5"/>
+        <v>74649600</v>
       </c>
     </row>
   </sheetData>
@@ -1177,5 +1455,6 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>